--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="人行月报资产端明细台账" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" concurrentCalc="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -26,6 +26,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -34,6 +35,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -49,6 +51,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -58,6 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -91,6 +95,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -99,6 +104,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -114,6 +120,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -122,6 +129,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -136,6 +144,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -144,6 +153,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -261,28 +271,35 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -290,18 +307,21 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -310,6 +330,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -382,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -391,9 +412,11 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -719,9 +742,10 @@
     <col min="18" max="18" width="13.08984375" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" customWidth="1"/>
-    <col min="23" max="23" width="11.6328125" customWidth="1"/>
-    <col min="24" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" customWidth="1"/>
+    <col min="21" max="22" width="8.7265625" style="8"/>
+    <col min="23" max="23" width="11.6328125" style="8" customWidth="1"/>
+    <col min="24" max="25" width="13" style="8" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" style="8" customWidth="1"/>
     <col min="27" max="28" width="20" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
@@ -824,12 +848,12 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -841,12 +865,12 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
@@ -858,12 +882,12 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
@@ -875,12 +899,12 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
@@ -892,12 +916,12 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
@@ -909,12 +933,12 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
@@ -926,12 +950,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
@@ -943,12 +967,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
@@ -960,12 +984,12 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
@@ -977,12 +1001,12 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
@@ -994,12 +1018,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
@@ -1011,12 +1035,12 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
@@ -1028,12 +1052,12 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
@@ -1045,12 +1069,12 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
@@ -1062,12 +1086,12 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
@@ -1079,12 +1103,12 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
@@ -1096,12 +1120,12 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
@@ -1113,12 +1137,12 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
@@ -1130,12 +1154,12 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
@@ -1147,12 +1171,12 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7"/>
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
@@ -1164,12 +1188,12 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7"/>
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
@@ -1181,12 +1205,12 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
@@ -1198,12 +1222,12 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
@@ -1215,12 +1239,12 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
@@ -1232,12 +1256,12 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
       <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
@@ -1249,12 +1273,12 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="7"/>
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
@@ -1266,12 +1290,12 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="2"/>
-      <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="2"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="7"/>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
@@ -1283,12 +1307,12 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="7"/>
       <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
@@ -1300,12 +1324,12 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="2"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="7"/>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
@@ -1317,12 +1341,12 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-      <c r="Z31" s="2"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="7"/>
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
@@ -1334,12 +1358,12 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="7"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
@@ -1351,12 +1375,12 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="2"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
@@ -1368,12 +1392,12 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="2"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="7"/>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
@@ -1385,12 +1409,12 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
-      <c r="X35" s="2"/>
-      <c r="Y35" s="2"/>
-      <c r="Z35" s="2"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="7"/>
       <c r="AA35" s="2"/>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
@@ -1402,12 +1426,12 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
-      <c r="Y36" s="2"/>
-      <c r="Z36" s="2"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="7"/>
       <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
@@ -1419,12 +1443,12 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-      <c r="Y37" s="2"/>
-      <c r="Z37" s="2"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
       <c r="AA37" s="2"/>
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
@@ -1436,12 +1460,12 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="7"/>
       <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
@@ -1453,12 +1477,12 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="2"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
       <c r="AA39" s="2"/>
       <c r="AB39" s="2"/>
       <c r="AC39" s="2"/>
@@ -1470,12 +1494,12 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="2"/>
-      <c r="W40" s="2"/>
-      <c r="X40" s="2"/>
-      <c r="Y40" s="2"/>
-      <c r="Z40" s="2"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
       <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
       <c r="AC40" s="2"/>
@@ -1487,12 +1511,12 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
-      <c r="Z41" s="2"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
       <c r="AA41" s="2"/>
       <c r="AB41" s="2"/>
       <c r="AC41" s="2"/>
@@ -1504,12 +1528,12 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="2"/>
-      <c r="X42" s="2"/>
-      <c r="Y42" s="2"/>
-      <c r="Z42" s="2"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
       <c r="AA42" s="2"/>
       <c r="AB42" s="2"/>
       <c r="AC42" s="2"/>
@@ -1521,12 +1545,12 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="2"/>
-      <c r="W43" s="2"/>
-      <c r="X43" s="2"/>
-      <c r="Y43" s="2"/>
-      <c r="Z43" s="2"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
       <c r="AA43" s="2"/>
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
@@ -1538,12 +1562,12 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="2"/>
-      <c r="W44" s="2"/>
-      <c r="X44" s="2"/>
-      <c r="Y44" s="2"/>
-      <c r="Z44" s="2"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
       <c r="AA44" s="2"/>
       <c r="AB44" s="2"/>
       <c r="AC44" s="2"/>
@@ -1555,12 +1579,12 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="2"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7"/>
       <c r="AA45" s="2"/>
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
@@ -1572,12 +1596,12 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="7"/>
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
@@ -1589,12 +1613,12 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="7"/>
       <c r="AA47" s="2"/>
       <c r="AB47" s="2"/>
       <c r="AC47" s="2"/>
@@ -1606,12 +1630,12 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="2"/>
-      <c r="W48" s="2"/>
-      <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="2"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7"/>
+      <c r="Y48" s="7"/>
+      <c r="Z48" s="7"/>
       <c r="AA48" s="2"/>
       <c r="AB48" s="2"/>
       <c r="AC48" s="2"/>
@@ -1623,12 +1647,12 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="7"/>
       <c r="AA49" s="2"/>
       <c r="AB49" s="2"/>
       <c r="AC49" s="2"/>
@@ -1640,12 +1664,12 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="7"/>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7"/>
+      <c r="Y50" s="7"/>
+      <c r="Z50" s="7"/>
       <c r="AA50" s="2"/>
       <c r="AB50" s="2"/>
       <c r="AC50" s="2"/>
@@ -1657,12 +1681,12 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="7"/>
       <c r="AA51" s="2"/>
       <c r="AB51" s="2"/>
       <c r="AC51" s="2"/>
@@ -1674,12 +1698,12 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="2"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7"/>
+      <c r="Y52" s="7"/>
+      <c r="Z52" s="7"/>
       <c r="AA52" s="2"/>
       <c r="AB52" s="2"/>
       <c r="AC52" s="2"/>
@@ -1691,12 +1715,12 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="2"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="7"/>
       <c r="AA53" s="2"/>
       <c r="AB53" s="2"/>
       <c r="AC53" s="2"/>
@@ -1708,12 +1732,12 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="2"/>
-      <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-      <c r="Z54" s="2"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
       <c r="AA54" s="2"/>
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
@@ -274,7 +274,7 @@
   <numFmts count="1">
     <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,15 +325,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -344,7 +335,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,18 +368,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -714,74 +704,74 @@
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="4"/>
-    <col min="23" max="23" width="11.6328125" style="4" customWidth="1"/>
-    <col min="24" max="25" width="13" style="4" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="4" customWidth="1"/>
+    <col min="21" max="22" width="8.7265625" style="2"/>
+    <col min="23" max="23" width="11.6328125" style="2" customWidth="1"/>
+    <col min="24" max="25" width="13" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" style="2" customWidth="1"/>
     <col min="27" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:30" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="U1" s="5" t="s">
@@ -802,16 +792,16 @@
       <c r="Z1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>产品名称</t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>成本</t>
-  </si>
-  <si>
-    <t>应计利息</t>
   </si>
   <si>
     <t>利息调整</t>
@@ -684,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -704,33 +701,33 @@
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="2"/>
-    <col min="23" max="23" width="11.6328125" style="2" customWidth="1"/>
-    <col min="24" max="25" width="13" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="2" customWidth="1"/>
-    <col min="27" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="8.7265625" style="1"/>
+    <col min="21" max="21" width="8.7265625" style="2"/>
+    <col min="22" max="22" width="11.6328125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="13" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" style="2" customWidth="1"/>
+    <col min="26" max="27" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>1</v>
@@ -739,40 +736,40 @@
         <v>0</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>3</v>
@@ -787,10 +784,10 @@
         <v>6</v>
       </c>
       <c r="Y1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="AA1" s="4" t="s">
         <v>8</v>
@@ -799,10 +796,7 @@
         <v>9</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailAsset001.xlsx
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>产品名称</t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>成本</t>
-  </si>
-  <si>
-    <t>利息调整</t>
   </si>
   <si>
     <t>公允价值变动</t>
@@ -681,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -702,32 +699,31 @@
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
     <col min="21" max="21" width="8.7265625" style="2"/>
-    <col min="22" max="22" width="11.6328125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="13" style="2" customWidth="1"/>
-    <col min="25" max="25" width="12.81640625" style="2" customWidth="1"/>
-    <col min="26" max="27" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.7265625" style="1"/>
+    <col min="22" max="23" width="13" style="2" customWidth="1"/>
+    <col min="24" max="24" width="12.81640625" style="2" customWidth="1"/>
+    <col min="25" max="26" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>1</v>
@@ -736,40 +732,40 @@
         <v>0</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>3</v>
@@ -781,10 +777,10 @@
         <v>5</v>
       </c>
       <c r="X1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>7</v>
@@ -793,10 +789,7 @@
         <v>8</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
